--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="149">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -373,12 +373,6 @@
   </si>
   <si>
     <t>Attaché de recherche clinique</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
   </si>
   <si>
     <t>365</t>
@@ -727,7 +721,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1219,23 +1213,15 @@
         <v>146</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>148</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
